--- a/data-manipulation-scripts/sheets-cleanup/sheets/KIT TRANSMISSÃO - 14_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/KIT TRANSMISSÃO - 14_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="165">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -25,6 +25,9 @@
     <t>PREÇO</t>
   </si>
   <si>
+    <t>8714.10.00</t>
+  </si>
+  <si>
     <t>7891799520137</t>
   </si>
   <si>
@@ -493,7 +496,7 @@
     <t>KIT TRANSMISSAO WURTH SUSUKI/ YES INTRUDER 125 2005 5527105</t>
   </si>
   <si>
-    <t>7895099121483</t>
+    <t>80</t>
   </si>
   <si>
     <t>KIT TRANSMISSAO IRON TITAN FAN160 2014 26825</t>
@@ -788,13 +791,16 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2">
         <v>5.0</v>
@@ -802,13 +808,16 @@
       <c r="D2" s="2">
         <v>360.0</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -816,13 +825,16 @@
       <c r="D3" s="2">
         <v>330.0</v>
       </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -830,13 +842,16 @@
       <c r="D4" s="2">
         <v>340.0</v>
       </c>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>1.0</v>
@@ -844,13 +859,16 @@
       <c r="D5" s="2">
         <v>160.0</v>
       </c>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -858,13 +876,16 @@
       <c r="D6" s="2">
         <v>160.0</v>
       </c>
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2">
         <v>2.0</v>
@@ -872,13 +893,16 @@
       <c r="D7" s="2">
         <v>350.0</v>
       </c>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2">
         <v>3.0</v>
@@ -886,13 +910,16 @@
       <c r="D8" s="2">
         <v>200.0</v>
       </c>
+      <c r="E8" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2">
         <v>3.0</v>
@@ -900,13 +927,16 @@
       <c r="D9" s="2">
         <v>220.0</v>
       </c>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2">
         <v>4.0</v>
@@ -914,13 +944,16 @@
       <c r="D10" s="2">
         <v>220.0</v>
       </c>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
@@ -928,37 +961,46 @@
       <c r="D11" s="2">
         <v>350.0</v>
       </c>
+      <c r="E11" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
       <c r="D12" s="3"/>
+      <c r="E12" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2">
         <v>3.0</v>
       </c>
       <c r="D13" s="3"/>
+      <c r="E13" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2">
         <v>4.0</v>
@@ -966,25 +1008,31 @@
       <c r="D14" s="2">
         <v>180.0</v>
       </c>
+      <c r="E14" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
       <c r="D15" s="3"/>
+      <c r="E15" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2">
         <v>3.0</v>
@@ -992,13 +1040,16 @@
       <c r="D16" s="2">
         <v>150.0</v>
       </c>
+      <c r="E16" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -1006,37 +1057,46 @@
       <c r="D17" s="2">
         <v>240.0</v>
       </c>
+      <c r="E17" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2">
         <v>9.0</v>
       </c>
       <c r="D18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
       <c r="D19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2">
         <v>5.0</v>
@@ -1044,385 +1104,481 @@
       <c r="D20" s="2">
         <v>220.0</v>
       </c>
+      <c r="E20" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2">
         <v>8.0</v>
       </c>
       <c r="D21" s="3"/>
+      <c r="E21" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2">
         <v>8.0</v>
       </c>
       <c r="D22" s="3"/>
+      <c r="E22" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2">
         <v>13.0</v>
       </c>
       <c r="D23" s="3"/>
+      <c r="E23" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2">
         <v>10.0</v>
       </c>
       <c r="D24" s="3"/>
+      <c r="E24" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25" s="2">
         <v>2.0</v>
       </c>
       <c r="D25" s="3"/>
+      <c r="E25" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
       </c>
       <c r="D26" s="3"/>
+      <c r="E26" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" s="2">
         <v>3.0</v>
       </c>
       <c r="D27" s="3"/>
+      <c r="E27" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="2">
         <v>7.0</v>
       </c>
       <c r="D28" s="3"/>
+      <c r="E28" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2">
         <v>1.0</v>
       </c>
       <c r="D29" s="3"/>
+      <c r="E29" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>1.0</v>
       </c>
       <c r="D30" s="3"/>
+      <c r="E30" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2">
         <v>9.0</v>
       </c>
       <c r="D31" s="3"/>
+      <c r="E31" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2">
         <v>1.0</v>
       </c>
       <c r="D32" s="3"/>
+      <c r="E32" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2">
         <v>1.0</v>
       </c>
       <c r="D33" s="3"/>
+      <c r="E33" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C34" s="2">
         <v>9.0</v>
       </c>
       <c r="D34" s="3"/>
+      <c r="E34" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>1.0</v>
       </c>
       <c r="D35" s="3"/>
+      <c r="E35" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="2">
         <v>2.0</v>
       </c>
       <c r="D36" s="3"/>
+      <c r="E36" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" s="2">
         <v>4.0</v>
       </c>
       <c r="D37" s="3"/>
+      <c r="E37" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2">
         <v>2.0</v>
       </c>
       <c r="D38" s="3"/>
+      <c r="E38" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="2">
         <v>5.0</v>
       </c>
       <c r="D39" s="3"/>
+      <c r="E39" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2">
         <v>4.0</v>
       </c>
       <c r="D40" s="3"/>
+      <c r="E40" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C41" s="2">
         <v>5.0</v>
       </c>
       <c r="D41" s="3"/>
+      <c r="E41" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C42" s="2">
         <v>1.0</v>
       </c>
       <c r="D42" s="3"/>
+      <c r="E42" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" s="2">
         <v>5.0</v>
       </c>
       <c r="D43" s="3"/>
+      <c r="E43" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" s="2">
         <v>2.0</v>
       </c>
       <c r="D44" s="3"/>
+      <c r="E44" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C45" s="2">
         <v>1.0</v>
       </c>
       <c r="D45" s="3"/>
+      <c r="E45" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" s="2">
         <v>1.0</v>
       </c>
       <c r="D46" s="3"/>
+      <c r="E46" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C47" s="2">
         <v>8.0</v>
       </c>
       <c r="D47" s="3"/>
+      <c r="E47" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C48" s="2">
         <v>4.0</v>
       </c>
       <c r="D48" s="3"/>
+      <c r="E48" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" s="2">
         <v>2.0</v>
       </c>
       <c r="D49" s="3"/>
+      <c r="E49" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C50" s="2">
         <v>4.0</v>
       </c>
       <c r="D50" s="3"/>
+      <c r="E50" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2">
         <v>1.0</v>
       </c>
       <c r="D51" s="3"/>
+      <c r="E51" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C52" s="2">
         <v>3.0</v>
@@ -1430,85 +1586,106 @@
       <c r="D52" s="2">
         <v>215.0</v>
       </c>
+      <c r="E52" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C53" s="2">
         <v>10.0</v>
       </c>
       <c r="D53" s="3"/>
+      <c r="E53" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C54" s="2">
         <v>1.0</v>
       </c>
       <c r="D54" s="3"/>
+      <c r="E54" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C55" s="2">
         <v>2.0</v>
       </c>
       <c r="D55" s="3"/>
+      <c r="E55" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C56" s="2">
         <v>2.0</v>
       </c>
       <c r="D56" s="3"/>
+      <c r="E56" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C57" s="2">
         <v>1.0</v>
       </c>
       <c r="D57" s="3"/>
+      <c r="E57" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C58" s="2">
         <v>11.0</v>
       </c>
       <c r="D58" s="3"/>
+      <c r="E58" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C59" s="2">
         <v>5.0</v>
@@ -1516,13 +1693,16 @@
       <c r="D59" s="2">
         <v>165.0</v>
       </c>
+      <c r="E59" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C60" s="2">
         <v>3.0</v>
@@ -1530,25 +1710,31 @@
       <c r="D60" s="2">
         <v>165.0</v>
       </c>
+      <c r="E60" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C61" s="2">
         <v>2.0</v>
       </c>
       <c r="D61" s="3"/>
+      <c r="E61" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C62" s="2">
         <v>3.0</v>
@@ -1556,13 +1742,16 @@
       <c r="D62" s="2">
         <v>290.0</v>
       </c>
+      <c r="E62" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C63" s="2">
         <v>1.0</v>
@@ -1570,13 +1759,16 @@
       <c r="D63" s="2">
         <v>145.0</v>
       </c>
+      <c r="E63" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2">
         <v>2.0</v>
@@ -1584,61 +1776,76 @@
       <c r="D64" s="2">
         <v>145.0</v>
       </c>
+      <c r="E64" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C65" s="2">
         <v>3.0</v>
       </c>
       <c r="D65" s="3"/>
+      <c r="E65" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C66" s="2">
         <v>1.0</v>
       </c>
       <c r="D66" s="3"/>
+      <c r="E66" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C67" s="2">
         <v>1.0</v>
       </c>
       <c r="D67" s="3"/>
+      <c r="E67" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C68" s="2">
         <v>2.0</v>
       </c>
       <c r="D68" s="3"/>
+      <c r="E68" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C69" s="2">
         <v>1.0</v>
@@ -1646,23 +1853,29 @@
       <c r="D69" s="2">
         <v>210.0</v>
       </c>
+      <c r="E69" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C70" s="2">
         <v>1.0</v>
       </c>
       <c r="D70" s="3"/>
+      <c r="E70" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4"/>
       <c r="B71" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C71" s="2">
         <v>1.0</v>
@@ -1670,150 +1883,189 @@
       <c r="D71" s="2">
         <v>180.0</v>
       </c>
+      <c r="E71" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C72" s="2">
         <v>10.0</v>
       </c>
       <c r="D72" s="3"/>
+      <c r="E72" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" s="2">
         <v>10.0</v>
       </c>
       <c r="D73" s="3"/>
+      <c r="E73" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C74" s="2">
         <v>2.0</v>
       </c>
       <c r="D74" s="3"/>
+      <c r="E74" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C75" s="2">
         <v>5.0</v>
       </c>
       <c r="D75" s="3"/>
+      <c r="E75" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C76" s="2">
         <v>9.0</v>
       </c>
       <c r="D76" s="3"/>
+      <c r="E76" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C77" s="2">
         <v>5.0</v>
       </c>
       <c r="D77" s="3"/>
+      <c r="E77" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C78" s="2">
         <v>4.0</v>
       </c>
       <c r="D78" s="3"/>
+      <c r="E78" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C79" s="2">
         <v>6.0</v>
       </c>
       <c r="D79" s="3"/>
+      <c r="E79" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C80" s="2">
         <v>13.0</v>
       </c>
       <c r="D80" s="3"/>
+      <c r="E80" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C81" s="2">
         <v>2.0</v>
       </c>
       <c r="D81" s="3"/>
+      <c r="E81" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C82" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D82" s="3"/>
+      <c r="E82" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C83" s="2">
         <v>1.0</v>
       </c>
       <c r="D83" s="3"/>
+      <c r="E83" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4"/>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/KIT TRANSMISSÃO - 14_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/KIT TRANSMISSÃO - 14_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="166">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -31,7 +31,7 @@
     <t>7891799520137</t>
   </si>
   <si>
-    <t>KIT TRASMISSAO W-MAX CB300 2009 A 2015 5876880034</t>
+    <t>KIT TRASMISSAO WURTH CB300 2009 A 2015 5876880034</t>
   </si>
   <si>
     <t>7909201065647</t>
@@ -97,19 +97,19 @@
     <t>7891799520113</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX XR300 2009 5986880030</t>
+    <t>KIT TRANSMISSAO WURTH XRE300 2009 5986880030</t>
   </si>
   <si>
     <t>7891799520106</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX XR300 2009 5986880029</t>
+    <t>KIT TRANSMISSAO WURTH XRE300 2009 5986880029</t>
   </si>
   <si>
     <t>7891799520038</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX NXR150 BROS 2003 A 2014 5986880017</t>
+    <t>KIT TRANSMISSAO WURTH NXR150 BROS 2003 A 2014 5986880017</t>
   </si>
   <si>
     <t>7895099123708</t>
@@ -139,13 +139,13 @@
     <t>7891799519988</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX TITAN160/ FAN160 2015 5986880006</t>
+    <t>KIT TRANSMISSAO WURTH TITAN160/ FAN160 2015 5986880006</t>
   </si>
   <si>
     <t>7891799520076</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO  W-MAX FAN 125 2009 5986880024</t>
+    <t>KIT TRANSMISSAO  WURTH FAN 125 2009 5986880024</t>
   </si>
   <si>
     <t>7899128875620</t>
@@ -187,7 +187,7 @@
     <t>789179954901</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX FACTOR 2020 5986880120</t>
+    <t>KIT TRANSMISSAO WURTH FACTOR 2020 5986880120</t>
   </si>
   <si>
     <t>6974288490324</t>
@@ -205,7 +205,7 @@
     <t>7891799545918</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX FAZER NOVA 2018 5986880115</t>
+    <t>KIT TRANSMISSAO WURTH FAZER NOVA 2018 5986880115</t>
   </si>
   <si>
     <t>7909201030560</t>
@@ -223,7 +223,7 @@
     <t>7891799520304</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX FAZER250 2005 A 2017</t>
+    <t>KIT TRANSMISSAO WURTH FAZER250 2005 A 2017</t>
   </si>
   <si>
     <t>789523003138</t>
@@ -271,82 +271,82 @@
     <t>7895099123609</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO IRON NXR150 122787</t>
+    <t>KIT TRANSMISSAO IRON BROS NXR150 122787</t>
   </si>
   <si>
     <t>7895099121490</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO IRON NXR160/ XRE190 026823</t>
+    <t>KIT TRANSMISSAO IRON BROS NXR160/ XRE190 026823</t>
   </si>
   <si>
     <t>7891579908254</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO COFAP NXR160/ XRE190 TMCC410014</t>
+    <t>KIT TRANSMISSAO COFAP BROS NXR160/ XRE190 TMCC410014</t>
   </si>
   <si>
     <t>7891799520069</t>
   </si>
   <si>
-    <t>KIT TRANSMISSA W-MAX NXR160 2014 5986880020</t>
+    <t>KIT TRANSMISSA WURTH BROS NXR160 2014 5986880020</t>
   </si>
   <si>
     <t>4043664001118</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO RIFFEL NXR160 2008 001-UNI-04900</t>
-  </si>
-  <si>
-    <t>KIT TRANSMISSAO W-MAX NXR150 2003 A 2014 5986880017</t>
+    <t>KIT TRANSMISSAO UNIK BROS NXR160 2008 001-UNI-04900</t>
+  </si>
+  <si>
+    <t>KIT TRANSMISSAO BROS WURTH BROS NXR150 2003 A 2014 5986880017</t>
   </si>
   <si>
     <t>7891799520045</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO C/ ANEL VEDACAO W-MAX NXR150 2004 A 2014 5986880018</t>
+    <t>KIT TRANSMISSAO C/ ANEL VEDACAO WURTH BROS NXR150 2004 A 2014 5986880018</t>
   </si>
   <si>
     <t>7899128802664</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO RIFFEL NXR150 2006 A 2015 71884</t>
+    <t>KIT TRANSMISSAO RIFFEL BROS NXR150 2006 A 2015 71884</t>
   </si>
   <si>
     <t>075320982575</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO IRON PREMIER NXR150 ESD 2012 17149</t>
+    <t>KIT TRANSMISSAO IRON PREMIER BROS NXR150 ESD 2012 17149</t>
   </si>
   <si>
     <t>7891799382933</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO WURTH NXR150 2003 A 2014 8500706</t>
+    <t>KIT TRANSMISSAO WURTH BROS NXR150 2003 A 2014 8500706</t>
   </si>
   <si>
     <t>7908073716879</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO SMARTFOX NXR150 2003 A 2015 41300-DF1-BR03</t>
+    <t>KIT TRANSMISSAO SMARTFOX BROS NXR150 2003 A 2015 41300-DF1-BR03</t>
   </si>
   <si>
     <t>7891799520168</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX POP110 2016 5986880037</t>
+    <t>KIT TRANSMISSAO WURTH POP110 2016 5986880037</t>
   </si>
   <si>
     <t>7891799520151</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX BIZ125/ POP100 2006 5986880036</t>
+    <t>KIT TRANSMISSAO WURTH BIZ125/ POP100 2006 5986880036</t>
   </si>
   <si>
     <t>404493001013</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO RIFFEL BIZ110 2016 001-UNI-06600</t>
+    <t>KIT TRANSMISSAO UNIK BIZ110 2016 001-UNI-06600</t>
   </si>
   <si>
     <t>7909201030256</t>
@@ -364,7 +364,7 @@
     <t>7891799520274</t>
   </si>
   <si>
-    <t>KIT TRANSMISSAO W-MAX XTZ250 LANDER 2009 5986880109</t>
+    <t>KIT TRANSMISSAO WURTH XTZ250 LANDER 2009 5986880109</t>
   </si>
   <si>
     <t>7895099125450</t>
@@ -446,6 +446,9 @@
   </si>
   <si>
     <t>KIT TRANSMISSAO GRAPKS TITAN 160 16873</t>
+  </si>
+  <si>
+    <t>KIT TRANSMISSAO IRON  BROS NXR150 122787</t>
   </si>
   <si>
     <t>4045816001014</t>
@@ -975,7 +978,9 @@
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2">
+        <v>350.0</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>4</v>
       </c>
@@ -990,7 +995,9 @@
       <c r="C13" s="2">
         <v>3.0</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2">
+        <v>180.0</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>4</v>
       </c>
@@ -1022,7 +1029,9 @@
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2">
+        <v>250.0</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>4</v>
       </c>
@@ -1071,7 +1080,9 @@
       <c r="C18" s="2">
         <v>9.0</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="2">
+        <v>150.0</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>4</v>
       </c>
@@ -1086,7 +1097,9 @@
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="2">
+        <v>250.0</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1131,9 @@
       <c r="C21" s="2">
         <v>8.0</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="2">
+        <v>210.0</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>4</v>
       </c>
@@ -1133,7 +1148,9 @@
       <c r="C22" s="2">
         <v>8.0</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="2">
+        <v>110.0</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>4</v>
       </c>
@@ -1148,7 +1165,9 @@
       <c r="C23" s="2">
         <v>13.0</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="2">
+        <v>120.0</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>4</v>
       </c>
@@ -1163,7 +1182,9 @@
       <c r="C24" s="2">
         <v>10.0</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="2">
+        <v>110.0</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>4</v>
       </c>
@@ -1178,7 +1199,9 @@
       <c r="C25" s="2">
         <v>2.0</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="2">
+        <v>125.0</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>4</v>
       </c>
@@ -1208,7 +1231,9 @@
       <c r="C27" s="2">
         <v>3.0</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>4</v>
       </c>
@@ -1223,7 +1248,9 @@
       <c r="C28" s="2">
         <v>7.0</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="2">
+        <v>100.0</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>4</v>
       </c>
@@ -1238,7 +1265,9 @@
       <c r="C29" s="2">
         <v>1.0</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="2">
+        <v>350.0</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>4</v>
       </c>
@@ -1253,7 +1282,9 @@
       <c r="C30" s="2">
         <v>1.0</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="2">
+        <v>350.0</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>4</v>
       </c>
@@ -1268,7 +1299,9 @@
       <c r="C31" s="2">
         <v>9.0</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="2">
+        <v>340.0</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1316,9 @@
       <c r="C32" s="2">
         <v>1.0</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="2">
+        <v>340.0</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>4</v>
       </c>
@@ -1298,7 +1333,9 @@
       <c r="C33" s="2">
         <v>1.0</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="2">
+        <v>260.0</v>
+      </c>
       <c r="E33" s="2" t="s">
         <v>4</v>
       </c>
@@ -1313,7 +1350,9 @@
       <c r="C34" s="2">
         <v>9.0</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="2">
+        <v>340.0</v>
+      </c>
       <c r="E34" s="2" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1367,9 @@
       <c r="C35" s="2">
         <v>1.0</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="2">
+        <v>226.0</v>
+      </c>
       <c r="E35" s="2" t="s">
         <v>4</v>
       </c>
@@ -1343,7 +1384,9 @@
       <c r="C36" s="2">
         <v>2.0</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="2">
+        <v>230.0</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>4</v>
       </c>
@@ -1358,7 +1401,9 @@
       <c r="C37" s="2">
         <v>4.0</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="2">
+        <v>130.0</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>4</v>
       </c>
@@ -1373,7 +1418,9 @@
       <c r="C38" s="2">
         <v>2.0</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="2">
+        <v>240.0</v>
+      </c>
       <c r="E38" s="2" t="s">
         <v>4</v>
       </c>
@@ -1388,7 +1435,9 @@
       <c r="C39" s="2">
         <v>5.0</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="2">
+        <v>260.0</v>
+      </c>
       <c r="E39" s="2" t="s">
         <v>4</v>
       </c>
@@ -1403,7 +1452,9 @@
       <c r="C40" s="2">
         <v>4.0</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="2">
+        <v>210.0</v>
+      </c>
       <c r="E40" s="2" t="s">
         <v>4</v>
       </c>
@@ -1418,7 +1469,9 @@
       <c r="C41" s="2">
         <v>5.0</v>
       </c>
-      <c r="D41" s="3"/>
+      <c r="D41" s="2">
+        <v>90.0</v>
+      </c>
       <c r="E41" s="2" t="s">
         <v>4</v>
       </c>
@@ -1433,7 +1486,9 @@
       <c r="C42" s="2">
         <v>1.0</v>
       </c>
-      <c r="D42" s="3"/>
+      <c r="D42" s="2">
+        <v>90.0</v>
+      </c>
       <c r="E42" s="2" t="s">
         <v>4</v>
       </c>
@@ -1448,7 +1503,9 @@
       <c r="C43" s="2">
         <v>5.0</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="2">
+        <v>90.0</v>
+      </c>
       <c r="E43" s="2" t="s">
         <v>4</v>
       </c>
@@ -1463,7 +1520,9 @@
       <c r="C44" s="2">
         <v>2.0</v>
       </c>
-      <c r="D44" s="3"/>
+      <c r="D44" s="2">
+        <v>210.0</v>
+      </c>
       <c r="E44" s="2" t="s">
         <v>4</v>
       </c>
@@ -1478,7 +1537,7 @@
       <c r="C45" s="2">
         <v>1.0</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1552,9 @@
       <c r="C46" s="2">
         <v>1.0</v>
       </c>
-      <c r="D46" s="3"/>
+      <c r="D46" s="2">
+        <v>130.0</v>
+      </c>
       <c r="E46" s="2" t="s">
         <v>4</v>
       </c>
@@ -1508,7 +1569,9 @@
       <c r="C47" s="2">
         <v>8.0</v>
       </c>
-      <c r="D47" s="3"/>
+      <c r="D47" s="2">
+        <v>142.0</v>
+      </c>
       <c r="E47" s="2" t="s">
         <v>4</v>
       </c>
@@ -1523,7 +1586,9 @@
       <c r="C48" s="2">
         <v>4.0</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="2">
+        <v>240.0</v>
+      </c>
       <c r="E48" s="2" t="s">
         <v>4</v>
       </c>
@@ -1538,7 +1603,9 @@
       <c r="C49" s="2">
         <v>2.0</v>
       </c>
-      <c r="D49" s="3"/>
+      <c r="D49" s="2">
+        <v>145.0</v>
+      </c>
       <c r="E49" s="2" t="s">
         <v>4</v>
       </c>
@@ -1553,7 +1620,9 @@
       <c r="C50" s="2">
         <v>4.0</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="2">
+        <v>120.0</v>
+      </c>
       <c r="E50" s="2" t="s">
         <v>4</v>
       </c>
@@ -1568,7 +1637,9 @@
       <c r="C51" s="2">
         <v>1.0</v>
       </c>
-      <c r="D51" s="3"/>
+      <c r="D51" s="2">
+        <v>140.0</v>
+      </c>
       <c r="E51" s="2" t="s">
         <v>4</v>
       </c>
@@ -1600,7 +1671,9 @@
       <c r="C53" s="2">
         <v>10.0</v>
       </c>
-      <c r="D53" s="3"/>
+      <c r="D53" s="2">
+        <v>100.0</v>
+      </c>
       <c r="E53" s="2" t="s">
         <v>4</v>
       </c>
@@ -1615,7 +1688,9 @@
       <c r="C54" s="2">
         <v>1.0</v>
       </c>
-      <c r="D54" s="3"/>
+      <c r="D54" s="2">
+        <v>120.0</v>
+      </c>
       <c r="E54" s="2" t="s">
         <v>4</v>
       </c>
@@ -1630,7 +1705,9 @@
       <c r="C55" s="2">
         <v>2.0</v>
       </c>
-      <c r="D55" s="3"/>
+      <c r="D55" s="2">
+        <v>120.0</v>
+      </c>
       <c r="E55" s="2" t="s">
         <v>4</v>
       </c>
@@ -1645,7 +1722,9 @@
       <c r="C56" s="2">
         <v>2.0</v>
       </c>
-      <c r="D56" s="3"/>
+      <c r="D56" s="2">
+        <v>125.0</v>
+      </c>
       <c r="E56" s="2" t="s">
         <v>4</v>
       </c>
@@ -1660,7 +1739,9 @@
       <c r="C57" s="2">
         <v>1.0</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="2">
+        <v>120.0</v>
+      </c>
       <c r="E57" s="2" t="s">
         <v>4</v>
       </c>
@@ -1675,7 +1756,9 @@
       <c r="C58" s="2">
         <v>11.0</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="2">
+        <v>225.0</v>
+      </c>
       <c r="E58" s="2" t="s">
         <v>4</v>
       </c>
@@ -1724,7 +1807,9 @@
       <c r="C61" s="2">
         <v>2.0</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="2">
+        <v>290.0</v>
+      </c>
       <c r="E61" s="2" t="s">
         <v>4</v>
       </c>
@@ -1790,7 +1875,9 @@
       <c r="C65" s="2">
         <v>3.0</v>
       </c>
-      <c r="D65" s="3"/>
+      <c r="D65" s="2">
+        <v>180.0</v>
+      </c>
       <c r="E65" s="2" t="s">
         <v>4</v>
       </c>
@@ -1805,7 +1892,9 @@
       <c r="C66" s="2">
         <v>1.0</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="2">
+        <v>190.0</v>
+      </c>
       <c r="E66" s="2" t="s">
         <v>4</v>
       </c>
@@ -1820,7 +1909,9 @@
       <c r="C67" s="2">
         <v>1.0</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="2">
+        <v>140.0</v>
+      </c>
       <c r="E67" s="2" t="s">
         <v>4</v>
       </c>
@@ -1835,7 +1926,9 @@
       <c r="C68" s="2">
         <v>2.0</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="2">
+        <v>180.0</v>
+      </c>
       <c r="E68" s="2" t="s">
         <v>4</v>
       </c>
@@ -1867,7 +1960,9 @@
       <c r="C70" s="2">
         <v>1.0</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="2">
+        <v>140.0</v>
+      </c>
       <c r="E70" s="2" t="s">
         <v>4</v>
       </c>
@@ -1897,7 +1992,9 @@
       <c r="C72" s="2">
         <v>10.0</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E72" s="2" t="s">
         <v>4</v>
       </c>
@@ -1907,162 +2004,184 @@
         <v>85</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="C73" s="2">
         <v>10.0</v>
       </c>
-      <c r="D73" s="3"/>
+      <c r="D73" s="2">
+        <v>90.0</v>
+      </c>
       <c r="E73" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2">
         <v>2.0</v>
       </c>
-      <c r="D74" s="3"/>
+      <c r="D74" s="2">
+        <v>140.0</v>
+      </c>
       <c r="E74" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C75" s="2">
         <v>5.0</v>
       </c>
-      <c r="D75" s="3"/>
+      <c r="D75" s="2">
+        <v>85.0</v>
+      </c>
       <c r="E75" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C76" s="2">
         <v>9.0</v>
       </c>
-      <c r="D76" s="3"/>
+      <c r="D76" s="2">
+        <v>130.0</v>
+      </c>
       <c r="E76" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C77" s="2">
         <v>5.0</v>
       </c>
-      <c r="D77" s="3"/>
+      <c r="D77" s="2">
+        <v>135.0</v>
+      </c>
       <c r="E77" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C78" s="2">
         <v>4.0</v>
       </c>
-      <c r="D78" s="3"/>
+      <c r="D78" s="2">
+        <v>85.0</v>
+      </c>
       <c r="E78" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C79" s="2">
         <v>6.0</v>
       </c>
-      <c r="D79" s="3"/>
+      <c r="D79" s="2">
+        <v>85.0</v>
+      </c>
       <c r="E79" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C80" s="2">
         <v>13.0</v>
       </c>
-      <c r="D80" s="3"/>
+      <c r="D80" s="2">
+        <v>85.0</v>
+      </c>
       <c r="E80" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C81" s="2">
         <v>2.0</v>
       </c>
-      <c r="D81" s="3"/>
+      <c r="D81" s="2">
+        <v>120.0</v>
+      </c>
       <c r="E81" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C82" s="2">
         <v>6.0</v>
       </c>
-      <c r="D82" s="3"/>
+      <c r="D82" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E82" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C83" s="2">
         <v>1.0</v>
       </c>
-      <c r="D83" s="3"/>
+      <c r="D83" s="2">
+        <v>90.0</v>
+      </c>
       <c r="E83" s="2" t="s">
         <v>4</v>
       </c>
